--- a/CHESS_Library/PSE_Templates/rubble_mound_pse.xlsx
+++ b/CHESS_Library/PSE_Templates/rubble_mound_pse.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\0_StormSim_Task\StormSim-Library\CHESS_Library\PSE_Templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\0_StormSim_Task\CHESS-Library\CHESS_Library\PSE_Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{56F9216B-970B-4E33-AC5F-2C6A36DD897D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD59B1C3-DDBE-44C7-9E0A-32231137CB3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{78425FC5-D8A0-4F22-AB02-535E95DBDA38}"/>
+    <workbookView xWindow="5325" yWindow="5325" windowWidth="28800" windowHeight="15270" xr2:uid="{78425FC5-D8A0-4F22-AB02-535E95DBDA38}"/>
   </bookViews>
   <sheets>
     <sheet name="rubble_mound_pse" sheetId="1" r:id="rId1"/>
@@ -1904,7 +1904,7 @@
         <v>53</v>
       </c>
       <c r="D12" s="18">
-        <v>176.45</v>
+        <v>0</v>
       </c>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
